--- a/site/exports/nwsuaf-humanities-social-development.xlsx
+++ b/site/exports/nwsuaf-humanities-social-development.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'总览'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'经历'!$A$1:$S$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'导师'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'论文'!$A$1:$L$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'来源'!$A$1:$G$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -453,8 +453,8 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
-    <col width="26.6" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
+    <col width="40.59999999999999" customWidth="1" min="8" max="8"/>
+    <col width="23.8" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
@@ -477,7 +477,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>官方主页</t>
+          <t>个人主页／职业网站（来源类型见说明）</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>缺项与冲突</t>
+          <t>来源说明与待核事项</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>替代官方职业报道（非个人主页）</t>
+          <t>替代职业资料来源（非已核个人主页）</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -622,11 +622,65 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>校区未标注</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>人文社会发展学院</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>未知（来源日期异常）</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Partial official professional biography, not full career or exhaustive bibliography.；Official appointment statement supports college affiliation, but independent directory and current employment remain unknown.；Bachelor/master labels and graduation do not independently establish awarded status; doctorate explicitly obtained. Study endpoints do not become conferral dates.；Educational subunits retained as institutional labels, not inferred declared majors.；Own advisors not stated in retained excerpts; no advisor inferred from coauthors or doctoral-student supervision title.；Source displayed date 2025-09-11 is not authenticated last modification or current personnel verification.；Selected works are official bibliographic claims with source-reported contribution roles; full texts and publisher metadata not verified. Second item year/full author list unknown.；Only necessary professional excerpts retained, not original HTTP bytes or full-page archive. Personal descriptors/contact information and metrics omitted.</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>官方资料（原来源）；公开个人页（访问与内容时效见来源记录）</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K3"/>
+  <autoFilter ref="A1:K4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -638,13 +692,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="46.2" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="25.2" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
@@ -720,7 +774,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>确证授位</t>
+          <t>来源记载学位</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -1401,8 +1455,329 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>理学学士</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>江南大学人文学院教育技术系</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2014-09</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：理学学士；来源level_as_source：本科；来源层次标签：本科</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>education_background</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>教育学硕士</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>陕西师范大学教育学部职业技术教育系</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：教育学硕士；来源level_as_source：硕士；来源层次标签：硕士</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>degree</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>社会学博士</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学人文社会科学学院社会学系</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源degree_as_source：社会学博士；来源level_as_source：博士；来源层次标签：博士</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>博士后</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>西安交通大学公共卫生学院</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr"/>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>Postdoctoral episode is nondegree; not denial of any qualification.；本轮按留存来源记录整理；学位资格为来源记载，不代表独立证书认证。；来源记载（episode_type）：博士后</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>employment</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>讲师</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学人文社会发展学院</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>至今</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>任职按留存来源表述保留；不据此认证当前人事状态。；来源role_as_source：讲师；来源institution_as_source：西北农林科技大学人文社会发展学院</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S16"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId2"/>
@@ -1414,6 +1789,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1516,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1527,7 +1907,7 @@
     <col width="51.8" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="64.39999999999999" customWidth="1" min="9" max="9"/>
+    <col width="65" customWidth="1" min="9" max="9"/>
     <col width="65" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -1803,8 +2183,112 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>One hundred‐year secular trends of overweight and obesity in China: effects of age, period, and cohort</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_profile</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源authors_as_source：Xie, J.&amp; Wang, Y.；来源person_contribution_role_as_source：第一作者；来源书目信息（卷）：32；来源书目信息（期）：11；来源书目信息（页码）：2186-2197</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>投资职业教育能否促进农村劳动力增收——基于倾向得分匹配（PSM）的反事实估计</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>journal_article_as_official_profile</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；source_attributed_recovery_not_reverified</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记载；本轮未重新核验原网页、出版元数据或全文。；来源person_contribution_role_as_source：第二作者</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L5"/>
+  <autoFilter ref="A1:L7"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
@@ -1814,6 +2298,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1825,14 +2313,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="51.8" customWidth="1" min="2" max="2"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
     <col width="65" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
@@ -2022,13 +2510,51 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>谢金辰</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>new-recovery-nwsuaf-xiejinchen-s001-157def1dcc7a</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://ch.nwafu.edu.cn/szdw/kjdw/9a3ede58c05d4c6bb40420e499ba7d3e.htm</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>留存来源记录（本轮重新审查；非独立证书认证）；NEW_RECOVERY：依据留存来源摘录、摘要或结构化记录；除另有本轮证据说明外未重新读取原网页，不继承旧核验结论。</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-25T06:16:10Z</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>nwsuaf</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>西北农林科技大学</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
